--- a/ARM Functions/Move Edits/False Swipe & Hold Back.xlsx
+++ b/ARM Functions/Move Edits/False Swipe & Hold Back.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05BE19D-CF35-4C00-90D9-AD0ADFCD6436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643E07F3-214E-43AF-A4F0-3F844C152DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="code" sheetId="12" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -116,21 +116,12 @@
     <t>mov r0, 0x3F</t>
   </si>
   <si>
-    <t>000C69B4</t>
-  </si>
-  <si>
     <t>10402DE9</t>
   </si>
   <si>
-    <t>6404FFEB</t>
-  </si>
-  <si>
     <t>5700A0E3</t>
   </si>
   <si>
-    <t>6004FFEB</t>
-  </si>
-  <si>
     <t>0210A0E3</t>
   </si>
   <si>
@@ -158,9 +149,6 @@
     <t>0300000A</t>
   </si>
   <si>
-    <t>D5F0FEEA</t>
-  </si>
-  <si>
     <t>30402DE9</t>
   </si>
   <si>
@@ -273,6 +261,18 @@
   </si>
   <si>
     <t>0C0090E5</t>
+  </si>
+  <si>
+    <t>000FEB98</t>
+  </si>
+  <si>
+    <t>EB23FEEB</t>
+  </si>
+  <si>
+    <t>E723FEEB</t>
+  </si>
+  <si>
+    <t>5C10FEEA</t>
   </si>
 </sst>
 </file>
@@ -732,14 +732,14 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
         <v>0210A0E3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -795,15 +795,15 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>23</v>
@@ -812,7 +812,7 @@
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="str">
         <f>DEC2HEX(HEX2DEC(A10)+4,8)</f>
-        <v>000C69B8</v>
+        <v>000FEB9C</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>14</v>
@@ -824,7 +824,7 @@
     <row r="12" spans="1:7">
       <c r="A12" s="4" t="str">
         <f t="shared" ref="A12:A24" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
-        <v>000C69BC</v>
+        <v>000FEBA0</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>15</v>
@@ -839,10 +839,10 @@
     <row r="13" spans="1:7">
       <c r="A13" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>000C69C0</v>
+        <v>000FEBA4</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>18</v>
@@ -852,7 +852,7 @@
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>000C69C4</v>
+        <v>000FEBA8</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>17</v>
@@ -865,40 +865,40 @@
     <row r="15" spans="1:7">
       <c r="A15" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>000C69C8</v>
+        <v>000FEBAC</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$24)</f>
-        <v>bne 0x000C69EC</v>
+        <v>bne 0x000FEBD0</v>
       </c>
       <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C69CC</v>
+        <v>000FEBB0</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="8"/>
       <c r="G16" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C69D0</v>
+        <v>000FEBB4</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>18</v>
@@ -908,7 +908,7 @@
     <row r="18" spans="1:8">
       <c r="A18" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C69D4</v>
+        <v>000FEBB8</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>22</v>
@@ -921,54 +921,54 @@
     <row r="19" spans="1:8">
       <c r="A19" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C69D8</v>
+        <v>000FEBBC</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C19" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",A$24)</f>
-        <v>beq 0x000C69EC</v>
+        <v>beq 0x000FEBD0</v>
       </c>
       <c r="D19" s="8"/>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>000C69DC</v>
+        <v>000FEBC0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>000C69E0</v>
+        <v>000FEBC4</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2">
         <v>0</v>
@@ -980,17 +980,17 @@
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>000C69E4</v>
+        <v>000FEBC8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C22" s="2" t="str">
         <f>SUBSTITUTE(C10,"push","pop")</f>
         <v>pop {r4, lr}</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -1002,16 +1002,16 @@
     <row r="23" spans="1:8">
       <c r="A23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>000C69E8</v>
+        <v>000FEBCC</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -1023,17 +1023,17 @@
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>000C69EC</v>
+        <v>000FEBD0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C24" s="2" t="str">
         <f>SUBSTITUTE(C22,"lr","pc")</f>
         <v>pop {r4, pc}</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G24" s="2">
         <v>2</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="F25" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2">
         <v>2</v>
@@ -1055,10 +1055,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2">
         <v>2</v>
@@ -1069,16 +1069,16 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2">
         <v>2</v>
@@ -1093,10 +1093,10 @@
         <v>00102DB0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1117,13 +1117,13 @@
         <v>00102DB8</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1132,7 +1132,7 @@
         <v>00102DBC</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>18</v>
@@ -1158,7 +1158,7 @@
         <v>00102DC4</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C33" s="12" t="str">
         <f>_xlfn.CONCAT("bne 0x",A43)</f>
@@ -1172,13 +1172,13 @@
         <v>00102DC8</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1187,10 +1187,10 @@
         <v>00102DCC</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1199,10 +1199,10 @@
         <v>00102DD0</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1223,7 +1223,7 @@
         <v>00102DD8</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C38" s="2" t="str">
         <f>_xlfn.CONCAT("beq 0x",A43)</f>
@@ -1236,13 +1236,13 @@
         <v>00102DDC</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1251,10 +1251,10 @@
         <v>00102DE0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1263,7 +1263,7 @@
         <v>00102DE4</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C41" s="2" t="str">
         <f>SUBSTITUTE(C27,"push","pop")</f>
@@ -1276,7 +1276,7 @@
         <v>00102DE8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>13</v>
@@ -1288,7 +1288,7 @@
         <v>00102DEC</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C43" s="2" t="str">
         <f>SUBSTITUTE(C41,"lr","pc")</f>
